--- a/AAII_Financials/Yearly/ELDN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELDN_YR_FIN.xlsx
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>55700</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>118100</v>
       </c>
       <c r="F76" s="3">
-        <v>7200</v>
+        <v>-48500</v>
       </c>
       <c r="G76" s="3">
         <v>84200</v>
